--- a/rules/CORE-000740/negative/01/data/unit-test-coreid-CG0287-negative.xlsx
+++ b/rules/CORE-000740/negative/01/data/unit-test-coreid-CG0287-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000740\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D39D0F-DF68-4E19-ADE0-AB2645D16862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0087E160-C9BE-4870-A677-21585A331EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="65">
   <si>
     <t>Product</t>
   </si>
@@ -218,9 +218,6 @@
   </si>
   <si>
     <t>["HLTSUBJI"]</t>
-  </si>
-  <si>
-    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -257,18 +254,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -316,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -327,7 +318,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -336,16 +327,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -706,8 +694,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -742,30 +734,10 @@
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>64</v>
       </c>
     </row>
@@ -776,7 +748,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -792,7 +764,7 @@
       <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -882,11 +854,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="9" t="s">
-        <v>65</v>
+      <c r="E5" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>36</v>
@@ -903,18 +875,18 @@
         <v>1</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="12" t="s">
-        <v>35</v>
+      <c r="E6" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -924,18 +896,18 @@
         <v>1</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="12" t="s">
-        <v>37</v>
+      <c r="E7" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -945,11 +917,11 @@
         <v>1</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="12" t="s">
-        <v>38</v>
+      <c r="E8" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>36</v>
@@ -966,11 +938,11 @@
         <v>1</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="12" t="s">
-        <v>39</v>
+      <c r="E9" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>36</v>
@@ -987,18 +959,18 @@
         <v>1</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="12" t="s">
-        <v>40</v>
+      <c r="E10" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -1008,18 +980,18 @@
         <v>1</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="12" t="s">
-        <v>41</v>
+      <c r="E11" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1029,11 +1001,11 @@
         <v>1</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="12" t="s">
-        <v>42</v>
+      <c r="E12" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>36</v>
@@ -1050,18 +1022,18 @@
         <v>1</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="12" t="s">
-        <v>43</v>
+      <c r="E13" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -1071,18 +1043,18 @@
         <v>1</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="12" t="s">
-        <v>44</v>
+      <c r="E14" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -1092,11 +1064,11 @@
         <v>1</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="12" t="s">
-        <v>45</v>
+      <c r="E15" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>36</v>
@@ -1113,11 +1085,11 @@
         <v>1</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="12" t="s">
-        <v>46</v>
+      <c r="E16" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>36</v>
@@ -1134,11 +1106,11 @@
         <v>1</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="12" t="s">
-        <v>47</v>
+      <c r="E17" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>36</v>
@@ -1155,11 +1127,11 @@
         <v>1</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="12" t="s">
-        <v>48</v>
+      <c r="E18" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>36</v>
@@ -1176,11 +1148,11 @@
         <v>1</v>
       </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="12" t="s">
-        <v>49</v>
+      <c r="E19" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>36</v>
@@ -1197,11 +1169,11 @@
         <v>1</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="12" t="s">
-        <v>50</v>
+      <c r="E20" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>36</v>
@@ -1218,11 +1190,11 @@
         <v>1</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="12" t="s">
-        <v>51</v>
+      <c r="E21" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>36</v>
@@ -1239,11 +1211,11 @@
         <v>1</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="12" t="s">
-        <v>52</v>
+      <c r="E22" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>36</v>
@@ -1260,18 +1232,18 @@
         <v>1</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="12" t="s">
-        <v>53</v>
+      <c r="E23" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -1281,18 +1253,18 @@
         <v>1</v>
       </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="12" t="s">
-        <v>54</v>
+      <c r="E24" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -1302,11 +1274,11 @@
         <v>1</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="12" t="s">
-        <v>55</v>
+      <c r="E25" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>36</v>
@@ -1323,11 +1295,11 @@
         <v>1</v>
       </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="12" t="s">
-        <v>56</v>
+      <c r="E26" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>36</v>
@@ -1344,11 +1316,11 @@
         <v>1</v>
       </c>
       <c r="D27" s="8"/>
-      <c r="E27" s="12" t="s">
-        <v>57</v>
+      <c r="E27" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>36</v>
@@ -1365,11 +1337,11 @@
         <v>1</v>
       </c>
       <c r="D28" s="8"/>
-      <c r="E28" s="12" t="s">
-        <v>58</v>
+      <c r="E28" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>36</v>
@@ -1386,11 +1358,11 @@
         <v>1</v>
       </c>
       <c r="D29" s="8"/>
-      <c r="E29" s="12" t="s">
-        <v>59</v>
+      <c r="E29" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>36</v>
@@ -1407,45 +1379,24 @@
         <v>1</v>
       </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="12" t="s">
-        <v>60</v>
+      <c r="E30" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="8">
-        <v>1</v>
-      </c>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
